--- a/reports/一级子公司A_现金流量表_2026-05.xlsx
+++ b/reports/一级子公司A_现金流量表_2026-05.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>157225380</v>
+        <v>154761131</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>731174340</v>
+        <v>720264900</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3086068</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>14366113</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1544504</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>7163570</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>769138</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>3591389</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>619444</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2866343</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>460575</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2153617</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>310048</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1434251</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>230279</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1075883</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>154873</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>717758</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>384528</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1791688</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>194077</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>902384</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>122636</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>569422</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>403142</v>
+        <v>396870</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1874806</v>
+        <v>1851475</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2864430</v>
+        <v>2836349</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>13320990</v>
+        <v>13132342</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>160492952</v>
+        <v>165870520</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>101846400</v>
+        <v>100055273</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>473635200</v>
+        <v>466698867</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1030830</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>4787327</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>770581</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3582160</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>513800</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2394475</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>386508</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1790974</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>256169</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1196970</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>194678</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>900515</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>16656130</v>
+        <v>16352122</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>77459090</v>
+        <v>76459785</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8487200</v>
+        <v>8410797</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>39469600</v>
+        <v>38922713</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3500970</v>
+        <v>3439670</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>16281210</v>
+        <v>16058879</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>130490700</v>
+        <v>131410428</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>30002252</v>
+        <v>34460092</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>185400</v>
+        <v>182138</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>927000</v>
+        <v>915824</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1545000</v>
+        <v>1516734</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>7725000</v>
+        <v>7620913</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>947600</v>
+        <v>938776</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>4738000</v>
+        <v>4676459</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1730400</v>
+        <v>1698872</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14420000</v>
+        <v>14200306</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>72100000</v>
+        <v>70973405</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2060000</v>
+        <v>2024347</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>10300000</v>
+        <v>10107332</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10300000</v>
+        <v>10117192</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>51500000</v>
+        <v>50742762</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>391400</v>
+        <v>384077</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1957000</v>
+        <v>1930782</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14811400</v>
+        <v>14584383</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-13081000</v>
+        <v>-12885511</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3605000</v>
+        <v>3556739</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>18025000</v>
+        <v>17780077</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5665000</v>
+        <v>5602540</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>28325000</v>
+        <v>27912692</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5665000</v>
+        <v>5570145</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>28325000</v>
+        <v>27984526</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>185400</v>
+        <v>183821</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>927000</v>
+        <v>914080</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9455400</v>
+        <v>9343100</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4635000</v>
+        <v>4597448</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>23175000</v>
+        <v>22868859</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4635000</v>
+        <v>4555130</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>23175000</v>
+        <v>22871251</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>741600</v>
+        <v>734434</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>3708000</v>
+        <v>3662119</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>648900</v>
+        <v>640750</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>3244500</v>
+        <v>3206314</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>92700</v>
+        <v>91612</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>463500</v>
+        <v>456895</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5469300</v>
+        <v>5423494</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3986100</v>
+        <v>3919606</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>20907352</v>
+        <v>25494187</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>20907352</v>
+        <v>25494187</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
